--- a/input/input.xlsx
+++ b/input/input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanmaygandhi/Box Sync/runModac/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6E9E4FF-16C3-1B49-9EE2-17AA1272776B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66AEC71D-7DB2-6C4F-AC8C-331C6905BA96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39800" yWindow="2220" windowWidth="27140" windowHeight="16940" xr2:uid="{0CDB0852-43DF-824B-975B-630A2C2414E7}"/>
+    <workbookView xWindow="45500" yWindow="2180" windowWidth="27140" windowHeight="16940" xr2:uid="{0CDB0852-43DF-824B-975B-630A2C2414E7}"/>
   </bookViews>
   <sheets>
     <sheet name="pos1" sheetId="1" r:id="rId1"/>
